--- a/xlsx/pages.unified.xlsx
+++ b/xlsx/pages.unified.xlsx
@@ -1,293 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17670" windowHeight="8985"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="17670" windowHeight="8985" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="元信息" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="元信息" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
-  <si>
-    <t>dir_path</t>
-  </si>
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>keywords</t>
-  </si>
-  <si>
-    <t>channel_intro</t>
-  </si>
-  <si>
-    <t>enabled</t>
-  </si>
-  <si>
-    <t>channel_intro_enabled</t>
-  </si>
-  <si>
-    <t>ad_slots</t>
-  </si>
-  <si>
-    <t>stat_ga4</t>
-  </si>
-  <si>
-    <t>stat_baidu</t>
-  </si>
-  <si>
-    <t>search_box</t>
-  </si>
-  <si>
-    <t>/</t>
-  </si>
-  <si>
-    <t>正协导航 - 让每一次寻找，都不止于找到</t>
-  </si>
-  <si>
-    <t>正协导航是独立第三方导航站：综合全品类导航，首页汇集政协与民主党派官方入口（按层级与组织分类陈列），另设政务导航、搜索工具等专题。本站为独立第三方，与任何官方机构无隶属关系。</t>
-  </si>
-  <si>
-    <t>正协导航,政协,人民政协,全国政协,政协官网,各省市政协,民主党派,民革,民盟,民建,民进,农工党,致公党,九三学社,台盟,政务导航,搜索工具</t>
-  </si>
-  <si>
-    <t>正协导航，一个独立的第三方导航站：综合导航各类官方与实用入口。首页为政协与民主党派专题——按层级与组织分类陈列，链接直达官网、域名可见。另设政务导航、搜索工具等专题。让每一次寻找，都不止于找到。</t>
-  </si>
-  <si>
-    <t>True</t>
-  </si>
-  <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>topics</t>
-  </si>
-  <si>
-    <t>专题导航 - 正协导航</t>
-  </si>
-  <si>
-    <t>正协导航全部专题导航：政务导航、搜索工具、政协专题等，一站直达各类导航。</t>
-  </si>
-  <si>
-    <t>专题导航,正协导航,政务导航,搜索工具,政协</t>
-  </si>
-  <si>
-    <t>topics/search</t>
-  </si>
-  <si>
-    <t>搜索工具 - 正协导航</t>
-  </si>
-  <si>
-    <t>正协导航搜索工具专题：聚合搜索引擎导航，在站内一键调用 Google、必应、百度、AI 对话、学术搜索等检索工具，方便快速查找。</t>
-  </si>
-  <si>
-    <t>搜索工具,搜索引擎,聚合搜索,Google,必应,百度,隐私搜索,学术搜索,AI对话</t>
-  </si>
-  <si>
-    <t>topics/gov</t>
-  </si>
-  <si>
-    <t>政务导航 - 正协导航</t>
-  </si>
-  <si>
-    <t>正协导航政务导航频道：汇集全国人民代表大会及地方各级人大官方入口，与国务院、国家政务服务平台及主要国务院组成部门官方入口，覆盖立法监督、宏观政策、民生办事与行业监管等权威政务信息，一键直达官方平台。</t>
-  </si>
-  <si>
-    <t>政务导航,人大,人民代表大会,国务院,政务机构,政府部门,官方入口,政务服务</t>
-  </si>
-  <si>
-    <t>本频道汇集两类权威政务官方入口：一是人民代表大会系统——从全国人民代表大会到地方各级人大；二是政务机构系统——国务院、国家政务服务平台及主要组成部门。所有链接均指向经核实的官方域名，帮你少走弯路、直达源头。</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -588,153 +472,153 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -788,11 +672,74 @@
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1079,178 +1026,327 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="14.5" customWidth="1"/>
-    <col min="2" max="2" width="20.75" customWidth="1"/>
-    <col min="3" max="3" width="21.5" customWidth="1"/>
-    <col min="5" max="5" width="19.75" customWidth="1"/>
-    <col min="7" max="7" width="10.5" customWidth="1"/>
-    <col min="8" max="8" width="5.875" customWidth="1"/>
-    <col min="9" max="9" width="9.375" customWidth="1"/>
-    <col min="11" max="11" width="10.75" customWidth="1"/>
+    <col width="14.5" customWidth="1" min="1" max="1"/>
+    <col width="20.75" customWidth="1" min="2" max="2"/>
+    <col width="21.5" customWidth="1" min="3" max="3"/>
+    <col width="19.75" customWidth="1" min="5" max="5"/>
+    <col width="10.5" customWidth="1" min="7" max="7"/>
+    <col width="5.875" customWidth="1" min="8" max="8"/>
+    <col width="9.375" customWidth="1" min="9" max="9"/>
+    <col width="10.75" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>dir_path</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>keywords</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>channel_intro</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>channel_intro_enabled</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ad_slots</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>stat_ga4</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>stat_baidu</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>search_box</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" t="s">
-        <v>16</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>正协导航 - 让每一次寻找，都不止于找到</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>正协导航是独立第三方导航站：综合全品类导航，首页汇集政协与民主党派官方入口（按层级与组织分类陈列），另设政务导航、搜索工具等专题。本站为独立第三方，与任何官方机构无隶属关系。</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>正协导航,政协,人民政协,全国政协,政协官网,各省市政协,民主党派,民革,民盟,民建,民进,农工党,致公党,九三学社,台盟,政务导航,搜索工具</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>正协导航，一个独立的第三方导航站：综合导航各类官方与实用入口。首页为政协与民主党派专题——按层级与组织分类陈列，链接直达官网、域名可见。另设政务导航、搜索工具等专题。让每一次寻找，都不止于找到。</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3"/>
-      <c r="I3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" t="s">
-        <v>16</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>topics</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>专题导航 - 正协导航</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>正协导航全部专题导航：政务导航、搜索工具、政协专题等，一站直达各类导航。</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>专题导航,正协导航,政务导航,搜索工具,政协</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" t="s">
-        <v>16</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>topics/search</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>搜索工具 - 正协导航</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>正协导航搜索工具专题：聚合搜索引擎导航，在站内一键调用 Google、必应、百度、AI 对话、学术搜索等检索工具，方便快速查找。</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>搜索工具,搜索引擎,聚合搜索,Google,必应,百度,隐私搜索,学术搜索,AI对话</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" t="s">
-        <v>16</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>topics/gov</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>政务导航 - 正协导航</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>正协导航政务导航频道：汇集全国人民代表大会及地方各级人大官方入口，与国务院、国家政务服务平台及主要国务院组成部门官方入口，覆盖立法监督、宏观政策、民生办事与行业监管等权威政务信息，一键直达官方平台。</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>政务导航,人大,人民代表大会,国务院,政务机构,政府部门,官方入口,政务服务</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>本频道汇集两类权威政务官方入口：一是人民代表大会系统——从全国人民代表大会到地方各级人大；二是政务机构系统——国务院、国家政务服务平台及主要组成部门。所有链接均指向经核实的官方域名，帮你少走弯路、直达源头。</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>topics/snh48</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SNH48 成员索引 - 正协导航</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>正协导航 SNH48 成员索引：收录 SNH48（上海）女子偶像组合现役成员，按 Team SII / NII / HII / X 及预备生分组陈列，每张卡片直达成员官方主页，方便粉丝快速查找与关注。</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SNH48,SNH48成员,SNH48成员索引,丝芭传媒,女子偶像组合,Team SII,Team NII,Team HII,Team X</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>本站为独立第三方粉丝索引站，与 SNH48 / 丝芭传媒无隶属关系。本频道按队伍整理 SNH48（上海）现役成员，每张卡片直达成员官方主页（snh48.com），仅供索引聚合，不代表本站立场。</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/xlsx/pages.unified.xlsx
+++ b/xlsx/pages.unified.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="17670" windowHeight="8985" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="元信息" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="元信息" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
     <col width="14.5" customWidth="1" min="1" max="1"/>
@@ -1346,6 +1346,58 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>topics/bankcode</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>联行号查询工具 - 正协导航</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>正协导航联行号查询工具专题：聚合各大银行官网的网点查询入口与各联行号查询工具，快速查到开户行行号（CNAPS号），方便转账汇款准确填单。</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>联行号查询,开户行行号,CNAPS号,银行联行号,网点查询,行号查询,支付系统行号</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>本站为独立第三方索引站，与任何银行或金融机构无隶属关系。本频道聚合联行号查询入口，仅作索引聚合，不代表本站立场，请以各机构官方公布信息为准。</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
